--- a/Daily_Report/Top 7 broker List with its Turnover 2024-09-24.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-09-24.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="274">
   <si>
     <t>Date: 2024-09-24</t>
   </si>
@@ -65,100 +65,100 @@
     <t>Sani Securities Company Limited</t>
   </si>
   <si>
+    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
+  </si>
+  <si>
     <t>Vision Securities Pvt.Limited</t>
   </si>
   <si>
-    <t>Shree Hari Securities Pvt.Ltd</t>
-  </si>
-  <si>
-    <t>Kumari Securities Pvt. Limited</t>
-  </si>
-  <si>
-    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
+    <t>Online Securities Pvt.Ltd</t>
   </si>
   <si>
     <t>Imperial Securities Co .Pvt.Limited</t>
   </si>
   <si>
+    <t>Stock Broker Opal Securities Investment Pvt. Limited</t>
+  </si>
+  <si>
     <t>58</t>
   </si>
   <si>
     <t>42</t>
   </si>
   <si>
+    <t>57</t>
+  </si>
+  <si>
     <t>34</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>57</t>
+    <t>49</t>
   </si>
   <si>
     <t>45</t>
   </si>
   <si>
-    <t>953,334,526.55</t>
-  </si>
-  <si>
-    <t>563,201,622.6</t>
-  </si>
-  <si>
-    <t>396,281,743.9</t>
-  </si>
-  <si>
-    <t>377,232,592.7</t>
-  </si>
-  <si>
-    <t>366,094,684.5</t>
-  </si>
-  <si>
-    <t>344,333,656.7</t>
-  </si>
-  <si>
-    <t>334,312,102.5</t>
-  </si>
-  <si>
-    <t>384,001,910.85</t>
-  </si>
-  <si>
-    <t>242,266,422.4</t>
-  </si>
-  <si>
-    <t>162,138,740.9</t>
-  </si>
-  <si>
-    <t>203,125,510.3</t>
-  </si>
-  <si>
-    <t>132,375,738.6</t>
-  </si>
-  <si>
-    <t>152,055,392.19</t>
-  </si>
-  <si>
-    <t>125,100,185.6</t>
-  </si>
-  <si>
-    <t>569,332,615.7</t>
-  </si>
-  <si>
-    <t>320,935,200.2</t>
-  </si>
-  <si>
-    <t>234,143,003.0</t>
-  </si>
-  <si>
-    <t>174,107,082.4</t>
-  </si>
-  <si>
-    <t>233,718,945.9</t>
-  </si>
-  <si>
-    <t>192,278,264.5</t>
-  </si>
-  <si>
-    <t>209,211,916.9</t>
+    <t>990,211,095.25</t>
+  </si>
+  <si>
+    <t>472,995,666.5</t>
+  </si>
+  <si>
+    <t>415,361,716.1</t>
+  </si>
+  <si>
+    <t>402,389,368.33</t>
+  </si>
+  <si>
+    <t>370,184,351.26</t>
+  </si>
+  <si>
+    <t>365,777,354.29</t>
+  </si>
+  <si>
+    <t>295,213,152.5</t>
+  </si>
+  <si>
+    <t>531,113,395.75</t>
+  </si>
+  <si>
+    <t>194,517,092.2</t>
+  </si>
+  <si>
+    <t>203,096,579.0</t>
+  </si>
+  <si>
+    <t>189,283,417.25</t>
+  </si>
+  <si>
+    <t>175,292,171.46</t>
+  </si>
+  <si>
+    <t>169,064,185.0</t>
+  </si>
+  <si>
+    <t>116,531,288.9</t>
+  </si>
+  <si>
+    <t>459,097,699.5</t>
+  </si>
+  <si>
+    <t>278,478,574.3</t>
+  </si>
+  <si>
+    <t>212,265,137.1</t>
+  </si>
+  <si>
+    <t>213,105,951.08</t>
+  </si>
+  <si>
+    <t>194,892,179.8</t>
+  </si>
+  <si>
+    <t>196,713,169.29</t>
+  </si>
+  <si>
+    <t>178,681,863.6</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -176,364 +176,331 @@
     <t>% of turnover</t>
   </si>
   <si>
+    <t>LICN</t>
+  </si>
+  <si>
+    <t>53,273,497.0</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>46,401,147.7</t>
+  </si>
+  <si>
+    <t>AHPC</t>
+  </si>
+  <si>
+    <t>27,940,876.1</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>25,775,954.9</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>24,635,510.8</t>
+  </si>
+  <si>
+    <t>HIDCLP</t>
+  </si>
+  <si>
+    <t>21,887,584.0</t>
+  </si>
+  <si>
+    <t>8,875,563.0</t>
+  </si>
+  <si>
+    <t>RURU</t>
+  </si>
+  <si>
+    <t>7,967,857.6</t>
+  </si>
+  <si>
+    <t>HLI</t>
+  </si>
+  <si>
+    <t>5,970,617.9</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>4,959,854.2</t>
+  </si>
+  <si>
+    <t>17,117,047.89</t>
+  </si>
+  <si>
+    <t>HIDCL</t>
+  </si>
+  <si>
+    <t>13,376,997.7</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>10,667,483.1</t>
+  </si>
+  <si>
+    <t>NGPL</t>
+  </si>
+  <si>
+    <t>10,563,522.5</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>8,304,584.0</t>
+  </si>
+  <si>
+    <t>7,449,397.0</t>
+  </si>
+  <si>
+    <t>ICFC</t>
+  </si>
+  <si>
+    <t>6,621,563.6</t>
+  </si>
+  <si>
+    <t>SCB</t>
+  </si>
+  <si>
+    <t>6,345,697.0</t>
+  </si>
+  <si>
+    <t>5,768,921.9</t>
+  </si>
+  <si>
+    <t>SARBTM</t>
+  </si>
+  <si>
+    <t>3,797,837.5</t>
+  </si>
+  <si>
+    <t>NLG</t>
+  </si>
+  <si>
+    <t>20,073,222.3</t>
+  </si>
+  <si>
+    <t>LSLPO</t>
+  </si>
+  <si>
+    <t>12,500,000.0</t>
+  </si>
+  <si>
+    <t>5,038,568.0</t>
+  </si>
+  <si>
+    <t>SICL</t>
+  </si>
+  <si>
+    <t>4,808,937.3</t>
+  </si>
+  <si>
+    <t>HDHPC</t>
+  </si>
+  <si>
+    <t>4,211,697.9</t>
+  </si>
+  <si>
+    <t>9,241,703.4</t>
+  </si>
+  <si>
+    <t>5,372,420.5</t>
+  </si>
+  <si>
+    <t>AKPL</t>
+  </si>
+  <si>
+    <t>5,129,010.59</t>
+  </si>
+  <si>
+    <t>GFCL</t>
+  </si>
+  <si>
+    <t>4,163,865.4</t>
+  </si>
+  <si>
+    <t>3,960,088.0</t>
+  </si>
+  <si>
+    <t>SRLI</t>
+  </si>
+  <si>
+    <t>60,721,203.1</t>
+  </si>
+  <si>
+    <t>3,353,584.2</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>2,101,275.2</t>
+  </si>
+  <si>
+    <t>CFCL</t>
+  </si>
+  <si>
+    <t>2,097,664.0</t>
+  </si>
+  <si>
+    <t>2,091,005.0</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>27,446,782.8</t>
+  </si>
+  <si>
+    <t>26,267,519.3</t>
+  </si>
+  <si>
+    <t>24,636,451.8</t>
+  </si>
+  <si>
+    <t>SBI</t>
+  </si>
+  <si>
+    <t>23,583,851.0</t>
+  </si>
+  <si>
+    <t>21,064,039.0</t>
+  </si>
+  <si>
+    <t>22,136,365.0</t>
+  </si>
+  <si>
+    <t>19,119,481.0</t>
+  </si>
+  <si>
+    <t>GBIME</t>
+  </si>
+  <si>
+    <t>9,522,599.19</t>
+  </si>
+  <si>
+    <t>9,138,579.19</t>
+  </si>
+  <si>
+    <t>CGH</t>
+  </si>
+  <si>
+    <t>9,020,155.69</t>
+  </si>
+  <si>
+    <t>10,182,810.0</t>
+  </si>
+  <si>
+    <t>6,425,117.7</t>
+  </si>
+  <si>
+    <t>5,902,303.2</t>
+  </si>
+  <si>
+    <t>CHDC</t>
+  </si>
+  <si>
+    <t>5,017,260.9</t>
+  </si>
+  <si>
+    <t>4,545,100.5</t>
+  </si>
+  <si>
+    <t>28,822,387.1</t>
+  </si>
+  <si>
+    <t>MKCL</t>
+  </si>
+  <si>
+    <t>7,071,493.1</t>
+  </si>
+  <si>
+    <t>6,534,804.9</t>
+  </si>
+  <si>
+    <t>4,878,702.4</t>
+  </si>
+  <si>
+    <t>GVL</t>
+  </si>
+  <si>
+    <t>4,383,765.0</t>
+  </si>
+  <si>
+    <t>STC</t>
+  </si>
+  <si>
+    <t>22,499,174.9</t>
+  </si>
+  <si>
+    <t>15,971,685.0</t>
+  </si>
+  <si>
     <t>CLI</t>
   </si>
   <si>
-    <t>67,801,950.0</t>
-  </si>
-  <si>
-    <t>USHL</t>
-  </si>
-  <si>
-    <t>66,922,493.3</t>
-  </si>
-  <si>
-    <t>AHPC</t>
-  </si>
-  <si>
-    <t>38,467,377.5</t>
-  </si>
-  <si>
-    <t>RFPL</t>
-  </si>
-  <si>
-    <t>21,811,165.0</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>11,814,550.0</t>
-  </si>
-  <si>
-    <t>RURU</t>
-  </si>
-  <si>
-    <t>35,651,776.0</t>
-  </si>
-  <si>
-    <t>NICA</t>
-  </si>
-  <si>
-    <t>24,894,350.6</t>
-  </si>
-  <si>
-    <t>CGH</t>
-  </si>
-  <si>
-    <t>20,883,852.0</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>12,540,000.0</t>
-  </si>
-  <si>
-    <t>SANIMA</t>
-  </si>
-  <si>
-    <t>12,041,244.4</t>
-  </si>
-  <si>
-    <t>SHEL</t>
-  </si>
-  <si>
-    <t>16,989,390.0</t>
-  </si>
-  <si>
-    <t>GCIL</t>
-  </si>
-  <si>
-    <t>13,686,706.1</t>
-  </si>
-  <si>
-    <t>PHCL</t>
-  </si>
-  <si>
-    <t>7,606,191.2</t>
-  </si>
-  <si>
-    <t>RLFL</t>
-  </si>
-  <si>
-    <t>5,722,359.0</t>
-  </si>
-  <si>
-    <t>NABIL</t>
-  </si>
-  <si>
-    <t>5,654,676.0</t>
-  </si>
-  <si>
-    <t>PFL</t>
-  </si>
-  <si>
-    <t>90,158,215.3</t>
-  </si>
-  <si>
-    <t>EHPL</t>
-  </si>
-  <si>
-    <t>36,542,239.0</t>
-  </si>
-  <si>
-    <t>17,649,197.0</t>
-  </si>
-  <si>
-    <t>GFCL</t>
-  </si>
-  <si>
-    <t>11,313,393.0</t>
-  </si>
-  <si>
-    <t>UPPER</t>
-  </si>
-  <si>
-    <t>10,914,840.0</t>
-  </si>
-  <si>
-    <t>NBL</t>
-  </si>
-  <si>
-    <t>80,662,100.0</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>7,488,270.0</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>5,494,855.0</t>
-  </si>
-  <si>
-    <t>NLIC</t>
-  </si>
-  <si>
-    <t>3,611,376.0</t>
-  </si>
-  <si>
-    <t>SONA</t>
-  </si>
-  <si>
-    <t>2,709,278.2</t>
-  </si>
-  <si>
-    <t>NGPL</t>
-  </si>
-  <si>
-    <t>18,704,040.5</t>
-  </si>
-  <si>
-    <t>17,101,268.0</t>
-  </si>
-  <si>
-    <t>RADHI</t>
-  </si>
-  <si>
-    <t>16,794,742.0</t>
-  </si>
-  <si>
-    <t>AKJCL</t>
-  </si>
-  <si>
-    <t>16,553,170.1</t>
-  </si>
-  <si>
-    <t>PRVU</t>
-  </si>
-  <si>
-    <t>15,956,930.0</t>
-  </si>
-  <si>
-    <t>26,932,846.5</t>
-  </si>
-  <si>
-    <t>BEDC</t>
-  </si>
-  <si>
-    <t>14,647,940.0</t>
-  </si>
-  <si>
-    <t>AKPL</t>
-  </si>
-  <si>
-    <t>7,435,025.0</t>
-  </si>
-  <si>
-    <t>5,543,295.0</t>
-  </si>
-  <si>
-    <t>3,616,463.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>STC</t>
-  </si>
-  <si>
-    <t>227,970,510.0</t>
-  </si>
-  <si>
-    <t>SJLIC</t>
-  </si>
-  <si>
-    <t>93,751,113.7</t>
-  </si>
-  <si>
-    <t>75,348,189.4</t>
-  </si>
-  <si>
-    <t>33,848,459.0</t>
-  </si>
-  <si>
-    <t>GBIME</t>
-  </si>
-  <si>
-    <t>15,523,744.9</t>
-  </si>
-  <si>
-    <t>NIFRA</t>
-  </si>
-  <si>
-    <t>110,120,475.8</t>
-  </si>
-  <si>
-    <t>ULHC</t>
-  </si>
-  <si>
-    <t>40,181,698.5</t>
-  </si>
-  <si>
-    <t>HATHY</t>
-  </si>
-  <si>
-    <t>28,379,859.6</t>
-  </si>
-  <si>
-    <t>26,751,052.7</t>
-  </si>
-  <si>
-    <t>10,238,964.4</t>
-  </si>
-  <si>
-    <t>42,830,237.0</t>
-  </si>
-  <si>
-    <t>HIDCLP</t>
-  </si>
-  <si>
-    <t>28,215,262.2</t>
-  </si>
-  <si>
-    <t>26,785,273.0</t>
-  </si>
-  <si>
-    <t>PMHPL</t>
-  </si>
-  <si>
-    <t>13,394,622.5</t>
-  </si>
-  <si>
-    <t>12,202,604.6</t>
-  </si>
-  <si>
-    <t>SGHC</t>
-  </si>
-  <si>
-    <t>55,726,790.4</t>
-  </si>
-  <si>
-    <t>ICFC</t>
-  </si>
-  <si>
-    <t>31,721,734.0</t>
-  </si>
-  <si>
-    <t>NRN</t>
-  </si>
-  <si>
-    <t>14,145,420.0</t>
-  </si>
-  <si>
-    <t>11,336,865.0</t>
-  </si>
-  <si>
-    <t>9,133,408.6</t>
-  </si>
-  <si>
-    <t>HIDCL</t>
-  </si>
-  <si>
-    <t>158,535,232.4</t>
-  </si>
-  <si>
-    <t>38,989,288.0</t>
-  </si>
-  <si>
-    <t>9,053,928.0</t>
-  </si>
-  <si>
-    <t>KBL</t>
-  </si>
-  <si>
-    <t>1,914,569.3</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>1,457,318.0</t>
-  </si>
-  <si>
-    <t>GILB</t>
-  </si>
-  <si>
-    <t>38,242,458.0</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>18,485,505.5</t>
-  </si>
-  <si>
-    <t>SRLI</t>
-  </si>
-  <si>
-    <t>15,337,597.6</t>
-  </si>
-  <si>
-    <t>10,194,810.0</t>
-  </si>
-  <si>
-    <t>8,951,764.8</t>
-  </si>
-  <si>
-    <t>39,247,429.0</t>
-  </si>
-  <si>
-    <t>29,687,517.4</t>
-  </si>
-  <si>
-    <t>BPCL</t>
-  </si>
-  <si>
-    <t>20,265,041.6</t>
-  </si>
-  <si>
-    <t>12,403,602.4</t>
-  </si>
-  <si>
-    <t>MLBL</t>
-  </si>
-  <si>
-    <t>12,201,961.5</t>
+    <t>7,031,924.9</t>
+  </si>
+  <si>
+    <t>6,878,111.1</t>
+  </si>
+  <si>
+    <t>CIT</t>
+  </si>
+  <si>
+    <t>6,703,587.0</t>
+  </si>
+  <si>
+    <t>ANLB</t>
+  </si>
+  <si>
+    <t>10,023,143.19</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>7,851,034.9</t>
+  </si>
+  <si>
+    <t>7,287,921.1</t>
+  </si>
+  <si>
+    <t>6,852,768.6</t>
+  </si>
+  <si>
+    <t>4,722,162.59</t>
+  </si>
+  <si>
+    <t>119,886,750.3</t>
+  </si>
+  <si>
+    <t>3,730,788.0</t>
+  </si>
+  <si>
+    <t>3,266,705.0</t>
+  </si>
+  <si>
+    <t>CYCL</t>
+  </si>
+  <si>
+    <t>2,388,205.1</t>
+  </si>
+  <si>
+    <t>MEN</t>
+  </si>
+  <si>
+    <t>2,250,121.0</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -551,106 +518,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>247,593,346.0</t>
-  </si>
-  <si>
-    <t>235,556,920.0</t>
-  </si>
-  <si>
-    <t>168,271,826.1</t>
-  </si>
-  <si>
-    <t>146,428,075.1</t>
-  </si>
-  <si>
-    <t>141,177,535.6</t>
+    <t>184,176,076.7</t>
+  </si>
+  <si>
+    <t>175,910,631.9</t>
+  </si>
+  <si>
+    <t>146,563,355.8</t>
+  </si>
+  <si>
+    <t>135,530,775.6</t>
+  </si>
+  <si>
+    <t>116,106,858.9</t>
+  </si>
+  <si>
+    <t>Hydro Power</t>
+  </si>
+  <si>
+    <t>1,431,213,117.3</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,365,899,018.7</t>
-  </si>
-  <si>
-    <t>Hydro Power</t>
-  </si>
-  <si>
-    <t>1,139,962,167.7</t>
+    <t>1,316,574,125.55</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>577,560,505.6</t>
+    <t>571,301,713.2</t>
+  </si>
+  <si>
+    <t>Commercial Banks</t>
+  </si>
+  <si>
+    <t>472,984,934.5</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>487,442,086.6</t>
-  </si>
-  <si>
-    <t>Commercial Banks</t>
-  </si>
-  <si>
-    <t>442,037,085.2</t>
+    <t>441,323,930.9</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>254,656,043.5</t>
+    <t>362,356,074.3</t>
+  </si>
+  <si>
+    <t>Non Life Insurance</t>
+  </si>
+  <si>
+    <t>303,993,227.3</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>240,138,161.3</t>
+    <t>300,007,083.8</t>
+  </si>
+  <si>
+    <t>Life Insurance</t>
+  </si>
+  <si>
+    <t>137,083,556.5</t>
+  </si>
+  <si>
+    <t>Manufacturing And Processing</t>
+  </si>
+  <si>
+    <t>124,236,353.4</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>81,719,009.09</t>
+  </si>
+  <si>
+    <t>Hotels And Tourism</t>
+  </si>
+  <si>
+    <t>77,362,684.09</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>Non Life Insurance</t>
-  </si>
-  <si>
-    <t>220,232,364.2</t>
-  </si>
-  <si>
-    <t>Manufacturing And Processing</t>
-  </si>
-  <si>
-    <t>139,930,280.8</t>
-  </si>
-  <si>
-    <t>Hotels And Tourism</t>
-  </si>
-  <si>
-    <t>101,949,658.3</t>
-  </si>
-  <si>
-    <t>Life Insurance</t>
-  </si>
-  <si>
-    <t>56,829,039.4</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>22,230,509.6</t>
+    <t>47,545,615.3</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>4,466,013.72</t>
+    <t>20,009,950.44</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>452,500.0</t>
+    <t>1,849,981.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -662,211 +632,211 @@
     <t>100%</t>
   </si>
   <si>
-    <t>185,108,050.75</t>
-  </si>
-  <si>
-    <t>112,590,732.6</t>
-  </si>
-  <si>
-    <t>23,999,704.5</t>
-  </si>
-  <si>
-    <t>13,841,847.7</t>
-  </si>
-  <si>
-    <t>13,598,907.6</t>
-  </si>
-  <si>
-    <t>67,895,124.8</t>
-  </si>
-  <si>
-    <t>49,588,176.1</t>
-  </si>
-  <si>
-    <t>39,992,488.6</t>
-  </si>
-  <si>
-    <t>23,530,008.1</t>
-  </si>
-  <si>
-    <t>21,790,803.2</t>
-  </si>
-  <si>
-    <t>59,208,217.5</t>
-  </si>
-  <si>
-    <t>43,961,802.3</t>
-  </si>
-  <si>
-    <t>22,355,147.1</t>
-  </si>
-  <si>
-    <t>14,732,380.7</t>
-  </si>
-  <si>
-    <t>7,407,104.9</t>
-  </si>
-  <si>
-    <t>111,426,945.3</t>
-  </si>
-  <si>
-    <t>73,582,564.8</t>
-  </si>
-  <si>
-    <t>7,997,560.8</t>
-  </si>
-  <si>
-    <t>5,413,838.6</t>
-  </si>
-  <si>
-    <t>1,451,808.0</t>
-  </si>
-  <si>
-    <t>82,670,386.09</t>
-  </si>
-  <si>
-    <t>16,253,428.0</t>
-  </si>
-  <si>
-    <t>14,511,783.5</t>
-  </si>
-  <si>
-    <t>7,674,470.0</t>
-  </si>
-  <si>
-    <t>3,672,260.0</t>
-  </si>
-  <si>
-    <t>94,914,687.7</t>
-  </si>
-  <si>
-    <t>21,716,379.2</t>
-  </si>
-  <si>
-    <t>17,554,807.1</t>
-  </si>
-  <si>
-    <t>5,950,996.0</t>
-  </si>
-  <si>
-    <t>2,362,972.0</t>
-  </si>
-  <si>
-    <t>37,940,769.0</t>
-  </si>
-  <si>
-    <t>34,513,737.79</t>
-  </si>
-  <si>
-    <t>26,985,822.5</t>
-  </si>
-  <si>
-    <t>6,137,418.1</t>
-  </si>
-  <si>
-    <t>4,444,027.2</t>
-  </si>
-  <si>
-    <t>136,454,241.19</t>
-  </si>
-  <si>
-    <t>121,903,578.6</t>
-  </si>
-  <si>
-    <t>34,514,330.0</t>
-  </si>
-  <si>
-    <t>14,107,628.8</t>
-  </si>
-  <si>
-    <t>113,577,227.6</t>
-  </si>
-  <si>
-    <t>106,254,478.2</t>
-  </si>
-  <si>
-    <t>53,130,546.6</t>
-  </si>
-  <si>
-    <t>17,515,137.1</t>
-  </si>
-  <si>
-    <t>14,854,042.2</t>
-  </si>
-  <si>
-    <t>57,940,984.0</t>
-  </si>
-  <si>
-    <t>52,189,938.6</t>
-  </si>
-  <si>
-    <t>48,625,916.8</t>
-  </si>
-  <si>
-    <t>26,926,803.0</t>
-  </si>
-  <si>
-    <t>13,797,374.0</t>
-  </si>
-  <si>
-    <t>64,703,897.2</t>
-  </si>
-  <si>
-    <t>49,769,751.8</t>
-  </si>
-  <si>
-    <t>27,819,975.3</t>
-  </si>
-  <si>
-    <t>15,856,891.5</t>
-  </si>
-  <si>
-    <t>3,614,208.1</t>
-  </si>
-  <si>
-    <t>159,434,703.19</t>
-  </si>
-  <si>
-    <t>48,201,706.0</t>
-  </si>
-  <si>
-    <t>9,318,018.0</t>
-  </si>
-  <si>
-    <t>5,687,194.6</t>
-  </si>
-  <si>
-    <t>3,195,425.7</t>
-  </si>
-  <si>
-    <t>57,455,311.5</t>
-  </si>
-  <si>
-    <t>47,181,607.8</t>
-  </si>
-  <si>
-    <t>46,965,384.6</t>
-  </si>
-  <si>
-    <t>14,564,099.5</t>
-  </si>
-  <si>
-    <t>7,571,040.3</t>
-  </si>
-  <si>
-    <t>90,213,392.6</t>
-  </si>
-  <si>
-    <t>40,048,954.7</t>
-  </si>
-  <si>
-    <t>29,811,217.4</t>
-  </si>
-  <si>
-    <t>16,014,093.7</t>
-  </si>
-  <si>
-    <t>13,422,539.0</t>
+    <t>132,302,449.1</t>
+  </si>
+  <si>
+    <t>87,248,344.75</t>
+  </si>
+  <si>
+    <t>72,938,902.4</t>
+  </si>
+  <si>
+    <t>54,907,293.5</t>
+  </si>
+  <si>
+    <t>50,183,259.0</t>
+  </si>
+  <si>
+    <t>62,907,486.0</t>
+  </si>
+  <si>
+    <t>59,461,337.0</t>
+  </si>
+  <si>
+    <t>14,531,965.8</t>
+  </si>
+  <si>
+    <t>14,008,381.9</t>
+  </si>
+  <si>
+    <t>12,514,186.6</t>
+  </si>
+  <si>
+    <t>68,252,498.3</t>
+  </si>
+  <si>
+    <t>48,246,996.5</t>
+  </si>
+  <si>
+    <t>21,395,412.89</t>
+  </si>
+  <si>
+    <t>18,732,636.3</t>
+  </si>
+  <si>
+    <t>13,965,794.6</t>
+  </si>
+  <si>
+    <t>47,614,067.3</t>
+  </si>
+  <si>
+    <t>46,033,171.5</t>
+  </si>
+  <si>
+    <t>24,330,819.6</t>
+  </si>
+  <si>
+    <t>23,347,270.5</t>
+  </si>
+  <si>
+    <t>9,218,549.19</t>
+  </si>
+  <si>
+    <t>48,861,687.0</t>
+  </si>
+  <si>
+    <t>35,022,848.6</t>
+  </si>
+  <si>
+    <t>27,395,110.6</t>
+  </si>
+  <si>
+    <t>12,872,378.2</t>
+  </si>
+  <si>
+    <t>11,966,029.7</t>
+  </si>
+  <si>
+    <t>60,427,702.1</t>
+  </si>
+  <si>
+    <t>37,878,458.0</t>
+  </si>
+  <si>
+    <t>15,067,249.1</t>
+  </si>
+  <si>
+    <t>12,434,964.9</t>
+  </si>
+  <si>
+    <t>11,970,020.2</t>
+  </si>
+  <si>
+    <t>73,301,746.8</t>
+  </si>
+  <si>
+    <t>14,253,697.9</t>
+  </si>
+  <si>
+    <t>6,785,561.0</t>
+  </si>
+  <si>
+    <t>5,082,605.8</t>
+  </si>
+  <si>
+    <t>4,512,913.0</t>
+  </si>
+  <si>
+    <t>141,213,493.19</t>
+  </si>
+  <si>
+    <t>74,007,073.2</t>
+  </si>
+  <si>
+    <t>53,846,102.5</t>
+  </si>
+  <si>
+    <t>46,926,966.5</t>
+  </si>
+  <si>
+    <t>27,377,682.3</t>
+  </si>
+  <si>
+    <t>105,651,207.9</t>
+  </si>
+  <si>
+    <t>58,564,009.1</t>
+  </si>
+  <si>
+    <t>26,389,454.3</t>
+  </si>
+  <si>
+    <t>21,457,802.39</t>
+  </si>
+  <si>
+    <t>21,217,108.8</t>
+  </si>
+  <si>
+    <t>57,400,060.0</t>
+  </si>
+  <si>
+    <t>40,387,213.79</t>
+  </si>
+  <si>
+    <t>28,844,320.0</t>
+  </si>
+  <si>
+    <t>16,956,588.3</t>
+  </si>
+  <si>
+    <t>15,471,485.2</t>
+  </si>
+  <si>
+    <t>77,452,519.2</t>
+  </si>
+  <si>
+    <t>52,349,296.5</t>
+  </si>
+  <si>
+    <t>20,613,883.0</t>
+  </si>
+  <si>
+    <t>13,135,913.0</t>
+  </si>
+  <si>
+    <t>11,846,723.6</t>
+  </si>
+  <si>
+    <t>48,061,312.3</t>
+  </si>
+  <si>
+    <t>34,286,338.9</t>
+  </si>
+  <si>
+    <t>19,684,425.89</t>
+  </si>
+  <si>
+    <t>14,063,473.5</t>
+  </si>
+  <si>
+    <t>54,668,072.5</t>
+  </si>
+  <si>
+    <t>47,599,447.2</t>
+  </si>
+  <si>
+    <t>30,005,127.5</t>
+  </si>
+  <si>
+    <t>16,297,303.9</t>
+  </si>
+  <si>
+    <t>9,841,154.4</t>
+  </si>
+  <si>
+    <t>130,541,881.8</t>
+  </si>
+  <si>
+    <t>17,469,221.2</t>
+  </si>
+  <si>
+    <t>6,153,506.0</t>
+  </si>
+  <si>
+    <t>5,330,695.3</t>
+  </si>
+  <si>
+    <t>4,235,740.4</t>
   </si>
 </sst>
 </file>
@@ -1463,17 +1433,17 @@
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="6" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="6" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -1675,7 +1645,7 @@
         <v>54</v>
       </c>
       <c r="D9" s="10">
-        <v>0.07112083755674609</v>
+        <v>0.05380014146029131</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>63</v>
@@ -1684,52 +1654,52 @@
         <v>64</v>
       </c>
       <c r="G9" s="12">
-        <v>0.06330197671557632</v>
+        <v>0.04627438589862853</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J9" s="14">
-        <v>0.04287199766711232</v>
+        <v>0.04120997972735407</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="M9" s="16">
-        <v>0.2389990076273703</v>
+        <v>0.01851290711510733</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="P9" s="18">
-        <v>0.2203312514907602</v>
+        <v>0.05422493477013975</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="S9" s="16">
-        <v>0.05431952449625294</v>
+        <v>0.02526592554626245</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="V9" s="18">
-        <v>0.08056198473999307</v>
+        <v>0.2056859682090215</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1741,61 +1711,61 @@
         <v>56</v>
       </c>
       <c r="D10" s="10">
-        <v>0.07019833168340628</v>
+        <v>0.04685985435083924</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>66</v>
-      </c>
       <c r="G10" s="12">
-        <v>0.04420148948626271</v>
+        <v>0.01876457572154099</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J10" s="14">
-        <v>0.03453781636595851</v>
+        <v>0.0322056587824272</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="M10" s="16">
-        <v>0.09686925177502033</v>
+        <v>0.01645561270040725</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P10" s="18">
-        <v>0.02045446251214281</v>
+        <v>0.03376695950937318</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="S10" s="16">
-        <v>0.04966481686366037</v>
+        <v>0.01468767936830932</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="V10" s="18">
-        <v>0.0438151652018042</v>
+        <v>0.01135987394735063</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1807,61 +1777,61 @@
         <v>58</v>
       </c>
       <c r="D11" s="10">
-        <v>0.04035034547548455</v>
+        <v>0.02821709051133761</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>68</v>
-      </c>
       <c r="G11" s="12">
-        <v>0.03708059629443262</v>
+        <v>0.01684551923902246</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J11" s="14">
-        <v>0.0191938975667761</v>
+        <v>0.02568239364995246</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M11" s="16">
-        <v>0.0467859812262717</v>
+        <v>0.01577004140625278</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="P11" s="18">
-        <v>0.0150093820878735</v>
+        <v>0.01361096973129787</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="S11" s="16">
-        <v>0.04877461634438014</v>
+        <v>0.01402222018352059</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="V11" s="18">
-        <v>0.02223977219011986</v>
+        <v>0.007117823790049463</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1873,61 +1843,61 @@
         <v>60</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02287881576987662</v>
+        <v>0.02603076760465131</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="G12" s="12">
+        <v>0.01262298647296381</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" s="14">
+        <v>0.02543210433350769</v>
+      </c>
+      <c r="K12" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="G12" s="12">
-        <v>0.02226556085209688</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="J12" s="14">
-        <v>0.01444012773256598</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>88</v>
-      </c>
       <c r="L12" s="15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02999049715992369</v>
+        <v>0.01433666581187826</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="P12" s="18">
-        <v>0.009864595562025976</v>
+        <v>0.01299065528737715</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="S12" s="16">
-        <v>0.04807305291803617</v>
+        <v>0.01138360631450889</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="V12" s="18">
-        <v>0.0165811975054059</v>
+        <v>0.007105591272733013</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1939,61 +1909,61 @@
         <v>62</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01239286910414899</v>
+        <v>0.02487904944529049</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>72</v>
-      </c>
       <c r="G13" s="12">
-        <v>0.02137998882959894</v>
+        <v>0.01048604575323313</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.0142693325822926</v>
+        <v>0.01999361924342743</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02893397922453692</v>
+        <v>0.009438215318068216</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="P13" s="18">
-        <v>0.007400484942031437</v>
+        <v>0.01137729859640097</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="S13" s="16">
-        <v>0.04634147632539576</v>
+        <v>0.01082649856136341</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01081762512620972</v>
+        <v>0.007083034689655299</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2004,7 +1974,7 @@
         <v>50</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>52</v>
@@ -2013,7 +1983,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>52</v>
@@ -2022,7 +1992,7 @@
         <v>50</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>52</v>
@@ -2031,7 +2001,7 @@
         <v>50</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>52</v>
@@ -2040,7 +2010,7 @@
         <v>50</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>52</v>
@@ -2049,7 +2019,7 @@
         <v>50</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>52</v>
@@ -2058,7 +2028,7 @@
         <v>50</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>52</v>
@@ -2067,566 +2037,566 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0.02771811276571333</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D16" s="10">
-        <v>0.2391296062936031</v>
-      </c>
-      <c r="E16" s="11" t="s">
+      <c r="G16" s="12">
+        <v>0.04680035477661189</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="G16" s="12">
-        <v>0.195525849679965</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>135</v>
-      </c>
       <c r="J16" s="14">
-        <v>0.1080802677874761</v>
+        <v>0.02451552371174345</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>142</v>
+        <v>63</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1477252800484225</v>
+        <v>0.07162810294819401</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="P16" s="18">
-        <v>0.4330443437509129</v>
+        <v>0.06077829822740843</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1110622132222139</v>
+        <v>0.02740230657377802</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1173975716299412</v>
+        <v>0.4061023341431239</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="10">
+        <v>0.02652719145039291</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="D17" s="10">
-        <v>0.09834020597079779</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>130</v>
-      </c>
       <c r="G17" s="12">
-        <v>0.0713451398000287</v>
+        <v>0.04042210606595484</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="J17" s="14">
-        <v>0.07120000513351935</v>
+        <v>0.0154687287030881</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="M17" s="16">
-        <v>0.08409065020854969</v>
+        <v>0.01757375730215779</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1065005575080946</v>
+        <v>0.04314521925531704</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="S17" s="16">
-        <v>0.05368486391124252</v>
+        <v>0.02146397202538528</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="V17" s="18">
-        <v>0.08880180280042359</v>
+        <v>0.01263760766891983</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C18" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="10">
+        <v>0.02487999974771036</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="10">
-        <v>0.07903646338360974</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>132</v>
-      </c>
       <c r="G18" s="12">
-        <v>0.0503902305341121</v>
+        <v>0.02013252948058458</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="J18" s="14">
-        <v>0.0675914886625692</v>
+        <v>0.01421003181376253</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="M18" s="16">
-        <v>0.0374978733909383</v>
+        <v>0.01624000387266892</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>98</v>
+        <v>143</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="P18" s="18">
-        <v>0.02473111023823128</v>
+        <v>0.01899573786970025</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>162</v>
+        <v>108</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="S18" s="16">
-        <v>0.04454283600096302</v>
+        <v>0.01992447321990826</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="V18" s="18">
-        <v>0.0606171342540613</v>
+        <v>0.01106558082638273</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="C19" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0.02381699327863596</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="D19" s="10">
-        <v>0.0355053321340342</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>133</v>
-      </c>
       <c r="G19" s="12">
-        <v>0.04749818116024725</v>
+        <v>0.01932064043550809</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="J19" s="14">
-        <v>0.03380075591718421</v>
+        <v>0.01207925695971478</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="M19" s="16">
-        <v>0.03005271871886164</v>
+        <v>0.01212433226118184</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="P19" s="18">
-        <v>0.005229710730749493</v>
+        <v>0.01858023192117362</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="S19" s="16">
-        <v>0.02960735844908187</v>
+        <v>0.01873480826417402</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>73</v>
+        <v>158</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="V19" s="18">
-        <v>0.03710186471636934</v>
+        <v>0.008089765241743421</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0.02127227123695472</v>
+      </c>
+      <c r="E20" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="F20" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="10">
-        <v>0.01628362811549322</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>134</v>
-      </c>
       <c r="G20" s="12">
-        <v>0.01817992702636791</v>
+        <v>0.01907027133408208</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="J20" s="14">
-        <v>0.03079274982467846</v>
+        <v>0.01094251184889112</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="M20" s="16">
-        <v>0.02421161049375042</v>
+        <v>0.01089433604618716</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="P20" s="18">
-        <v>0.003980713355590936</v>
+        <v>0.01810878006372484</v>
       </c>
       <c r="Q20" s="15" t="s">
         <v>57</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="S20" s="16">
-        <v>0.02599735641816509</v>
+        <v>0.01290993700024447</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="V20" s="18">
-        <v>0.03649871305511591</v>
+        <v>0.007622021515453991</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>150</v>
+        <v>89</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2400710587458425</v>
+        <v>0.2515506956642846</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2003602907559104</v>
+        <v>0.2314016921536355</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1015123081361769</v>
+        <v>0.1004122598182797</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D34" s="22">
-        <v>0.08567305211092369</v>
+        <v>0.08313205620743444</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D35" s="22">
-        <v>0.07769264755010265</v>
+        <v>0.07756730321241281</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="D36" s="22">
-        <v>0.04475846687206666</v>
+        <v>0.06368787531817864</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="D37" s="22">
-        <v>0.042206797017425</v>
+        <v>0.05342999367474144</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D38" s="22">
-        <v>0.04140159587575646</v>
+        <v>0.05272938720438271</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D39" s="22">
-        <v>0.03870814468694366</v>
+        <v>0.02409387084626691</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D40" s="22">
-        <v>0.02459421245812997</v>
+        <v>0.02183584034187772</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01791872025074899</v>
+        <v>0.01436297176124337</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="D42" s="22">
-        <v>0.009988298892880079</v>
+        <v>0.01359730201503742</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="D43" s="22">
-        <v>0.003907244901025724</v>
+        <v>0.00835663987419594</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D44" s="22">
-        <v>0.0007849486893657791</v>
+        <v>0.003516958370871869</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="D45" s="22">
-        <v>7.953161441310998E-05</v>
+        <v>0.0003251535371570821</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -2799,17 +2769,17 @@
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="6" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="6" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -3005,331 +2975,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="D9" s="10">
+        <v>0.1336103480708802</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="G9" s="12">
+        <v>0.1329980176467431</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="I9" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="D9" s="10">
-        <v>0.1941690409765008</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="F9" s="11" t="s">
+      <c r="J9" s="14">
+        <v>0.1643206286338819</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="G9" s="12">
-        <v>0.1205520759804714</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="I9" s="13" t="s">
+      <c r="M9" s="16">
+        <v>0.1183283432601819</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="O9" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="J9" s="14">
-        <v>0.1494093997803264</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="L9" s="15" t="s">
+      <c r="P9" s="18">
+        <v>0.1319928485190933</v>
+      </c>
+      <c r="Q9" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="R9" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="M9" s="16">
-        <v>0.295379952465067</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="O9" s="17" t="s">
+      <c r="S9" s="16">
+        <v>0.1652035080665245</v>
+      </c>
+      <c r="T9" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="U9" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="P9" s="18">
-        <v>0.2258169528271312</v>
-      </c>
-      <c r="Q9" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="R9" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="S9" s="16">
-        <v>0.2756474304883134</v>
-      </c>
-      <c r="T9" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="U9" s="17" t="s">
-        <v>245</v>
-      </c>
       <c r="V9" s="18">
-        <v>0.1134890681978825</v>
+        <v>0.2483010874659455</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0.08811085350237596</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.1257122236235118</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="I10" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="D10" s="10">
-        <v>0.118102019243394</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="F10" s="11" t="s">
+      <c r="J10" s="14">
+        <v>0.1161565802284588</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="G10" s="12">
-        <v>0.08804693401108819</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="I10" s="13" t="s">
+      <c r="M10" s="16">
+        <v>0.1143995719644564</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="O10" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="J10" s="14">
-        <v>0.1109357243342847</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="L10" s="15" t="s">
+      <c r="P10" s="18">
+        <v>0.09460920884632859</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="R10" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="M10" s="16">
-        <v>0.1950588740843972</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="O10" s="17" t="s">
+      <c r="S10" s="16">
+        <v>0.1035560500280965</v>
+      </c>
+      <c r="T10" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="U10" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="P10" s="18">
-        <v>0.04439678773866491</v>
-      </c>
-      <c r="Q10" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="R10" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="S10" s="16">
-        <v>0.06306783777143328</v>
-      </c>
-      <c r="T10" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="U10" s="17" t="s">
-        <v>246</v>
-      </c>
       <c r="V10" s="18">
-        <v>0.1032380746670695</v>
+        <v>0.04828273327015808</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C11" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0.07365995266048299</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="G11" s="12">
+        <v>0.03072325357128827</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="I11" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="D11" s="10">
-        <v>0.02517448370075504</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="F11" s="11" t="s">
+      <c r="J11" s="14">
+        <v>0.05151031515588443</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="G11" s="12">
-        <v>0.07100918568979989</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="I11" s="13" t="s">
+      <c r="M11" s="16">
+        <v>0.06046586096689877</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="O11" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="J11" s="14">
-        <v>0.05641225578547274</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="L11" s="15" t="s">
+      <c r="P11" s="18">
+        <v>0.07400396723080001</v>
+      </c>
+      <c r="Q11" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="R11" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="M11" s="16">
-        <v>0.02120060926538281</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="O11" s="17" t="s">
+      <c r="S11" s="16">
+        <v>0.04119240549827533</v>
+      </c>
+      <c r="T11" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="U11" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="P11" s="18">
-        <v>0.03963942694174791</v>
-      </c>
-      <c r="Q11" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="R11" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="S11" s="16">
-        <v>0.05098196693358556</v>
-      </c>
-      <c r="T11" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="U11" s="17" t="s">
-        <v>247</v>
-      </c>
       <c r="V11" s="18">
-        <v>0.08072044744476459</v>
+        <v>0.0229852936515083</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C12" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="D12" s="10">
+        <v>0.05545008914098006</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0.02961630072355008</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I12" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="D12" s="10">
-        <v>0.01451940249147583</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="F12" s="11" t="s">
+      <c r="J12" s="14">
+        <v>0.04509957363400829</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="L12" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="G12" s="12">
-        <v>0.0417790133334037</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="I12" s="13" t="s">
+      <c r="M12" s="16">
+        <v>0.05802158888266867</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="O12" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="J12" s="14">
-        <v>0.03717653141174643</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="L12" s="15" t="s">
+      <c r="P12" s="18">
+        <v>0.03477288587749904</v>
+      </c>
+      <c r="Q12" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="R12" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="M12" s="16">
-        <v>0.01435146035831914</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="O12" s="17" t="s">
+      <c r="S12" s="16">
+        <v>0.03399599443256174</v>
+      </c>
+      <c r="T12" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="U12" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="P12" s="18">
-        <v>0.02096307410330619</v>
-      </c>
-      <c r="Q12" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="R12" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="S12" s="16">
-        <v>0.01728264398267868</v>
-      </c>
-      <c r="T12" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="U12" s="17" t="s">
-        <v>248</v>
-      </c>
       <c r="V12" s="18">
-        <v>0.01835834854348415</v>
+        <v>0.01721673223892015</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C13" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D13" s="10">
+        <v>0.05067935437274631</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0.02645729651732443</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="I13" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="D13" s="10">
-        <v>0.01426457053770282</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="F13" s="11" t="s">
+      <c r="J13" s="14">
+        <v>0.03362321094763022</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="L13" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="G13" s="12">
-        <v>0.03869094534813934</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="I13" s="13" t="s">
+      <c r="M13" s="16">
+        <v>0.02290952476766199</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="O13" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="J13" s="14">
-        <v>0.01869151181960366</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="L13" s="15" t="s">
+      <c r="P13" s="18">
+        <v>0.03232451522942856</v>
+      </c>
+      <c r="Q13" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="R13" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="M13" s="16">
-        <v>0.003848575197622365</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="O13" s="17" t="s">
+      <c r="S13" s="16">
+        <v>0.03272488047608815</v>
+      </c>
+      <c r="T13" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="U13" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="P13" s="18">
-        <v>0.01003090226512152</v>
-      </c>
-      <c r="Q13" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="R13" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="S13" s="16">
-        <v>0.006862448540889323</v>
-      </c>
-      <c r="T13" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="U13" s="17" t="s">
-        <v>249</v>
-      </c>
       <c r="V13" s="18">
-        <v>0.01329304912017058</v>
+        <v>0.01528696456029343</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3340,7 +3310,7 @@
         <v>50</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>52</v>
@@ -3349,7 +3319,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>52</v>
@@ -3358,7 +3328,7 @@
         <v>50</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>52</v>
@@ -3367,7 +3337,7 @@
         <v>50</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>52</v>
@@ -3376,7 +3346,7 @@
         <v>50</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>52</v>
@@ -3385,7 +3355,7 @@
         <v>50</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>52</v>
@@ -3394,7 +3364,7 @@
         <v>50</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>52</v>
@@ -3403,331 +3373,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="D16" s="10">
-        <v>0.2391296062936031</v>
+        <v>0.1426094838538924</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="G16" s="12">
-        <v>0.2016635305056026</v>
+        <v>0.2233661223194315</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1462115903442203</v>
+        <v>0.1381929479176668</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="L16" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="M16" s="16">
+        <v>0.1924815248510271</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="O16" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="P16" s="18">
+        <v>0.1298307509121152</v>
+      </c>
+      <c r="Q16" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="R16" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="M16" s="16">
-        <v>0.1715225525368556</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="O16" s="17" t="s">
+      <c r="S16" s="16">
+        <v>0.1494572363729697</v>
+      </c>
+      <c r="T16" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="U16" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="P16" s="18">
-        <v>0.4355012786316486</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="R16" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="S16" s="16">
-        <v>0.1668594120326083</v>
-      </c>
-      <c r="T16" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="U16" s="17" t="s">
-        <v>279</v>
-      </c>
       <c r="V16" s="18">
-        <v>0.2698478216175258</v>
+        <v>0.4421953449380952</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1431336402907918</v>
+        <v>0.07473868304951212</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="G17" s="12">
-        <v>0.1886615271267864</v>
+        <v>0.1238151070883014</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1316990737104708</v>
+        <v>0.09723383796468284</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="L17" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M17" s="16">
+        <v>0.1300961223634226</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="O17" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="P17" s="18">
+        <v>0.09261963338887573</v>
+      </c>
+      <c r="Q17" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="R17" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="M17" s="16">
-        <v>0.1319338592770539</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="O17" s="17" t="s">
+      <c r="S17" s="16">
+        <v>0.1301322967147432</v>
+      </c>
+      <c r="T17" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="U17" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="P17" s="18">
-        <v>0.1316645885362479</v>
-      </c>
-      <c r="Q17" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="R17" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="S17" s="16">
-        <v>0.1370229336631675</v>
-      </c>
-      <c r="T17" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="U17" s="17" t="s">
-        <v>280</v>
-      </c>
       <c r="V17" s="18">
-        <v>0.1197951088234983</v>
+        <v>0.05917494207850377</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="D18" s="10">
-        <v>0.1278707265970467</v>
+        <v>0.05437840755198304</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="G18" s="12">
-        <v>0.09433663623823516</v>
+        <v>0.05579216929252776</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="J18" s="14">
-        <v>0.1227054174170348</v>
+        <v>0.06944385792419928</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="L18" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="M18" s="16">
+        <v>0.0512286969348915</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="O18" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="P18" s="18">
+        <v>0.06077829822740843</v>
+      </c>
+      <c r="Q18" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="R18" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="M18" s="16">
-        <v>0.07374753888809459</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="O18" s="17" t="s">
+      <c r="S18" s="16">
+        <v>0.08203112398317304</v>
+      </c>
+      <c r="T18" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="U18" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="P18" s="18">
-        <v>0.02545248099607412</v>
-      </c>
-      <c r="Q18" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="R18" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="S18" s="16">
-        <v>0.1363949869150273</v>
-      </c>
-      <c r="T18" s="17" t="s">
-        <v>200</v>
-      </c>
-      <c r="U18" s="17" t="s">
-        <v>281</v>
-      </c>
       <c r="V18" s="18">
-        <v>0.08917181632693061</v>
+        <v>0.02084428131974913</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="D19" s="10">
-        <v>0.03620379734373316</v>
+        <v>0.04739087122443551</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="G19" s="12">
-        <v>0.03109923053691145</v>
+        <v>0.0453657483984581</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="I19" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="J19" s="14">
+        <v>0.04082366680110122</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="L19" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="M19" s="16">
+        <v>0.03264478148246507</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="O19" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="J19" s="14">
-        <v>0.06794863355298765</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="L19" s="15" t="s">
+      <c r="P19" s="18">
+        <v>0.05317465698644454</v>
+      </c>
+      <c r="Q19" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="R19" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="M19" s="16">
-        <v>0.04203478651329164</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="O19" s="17" t="s">
+      <c r="S19" s="16">
+        <v>0.04455525665779456</v>
+      </c>
+      <c r="T19" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="U19" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="P19" s="18">
-        <v>0.01553476420387633</v>
-      </c>
-      <c r="Q19" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="R19" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="S19" s="16">
-        <v>0.04229647383174321</v>
-      </c>
-      <c r="T19" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="U19" s="17" t="s">
-        <v>282</v>
-      </c>
       <c r="V19" s="18">
-        <v>0.04790162719281154</v>
+        <v>0.01805710638180323</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01479819350617015</v>
+        <v>0.02764832916065025</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="G20" s="12">
-        <v>0.0263742887164047</v>
+        <v>0.04485687777437598</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="I20" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0.03724822149057949</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="M20" s="16">
+        <v>0.02944094584100564</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="O20" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="J20" s="14">
-        <v>0.03481708206947254</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="L20" s="15" t="s">
+      <c r="P20" s="18">
+        <v>0.03799045921885142</v>
+      </c>
+      <c r="Q20" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="R20" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="M20" s="16">
-        <v>0.009580847917015098</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="O20" s="17" t="s">
+      <c r="S20" s="16">
+        <v>0.02690476675108109</v>
+      </c>
+      <c r="T20" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="U20" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="P20" s="18">
-        <v>0.008728413263809626</v>
-      </c>
-      <c r="Q20" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="R20" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="S20" s="16">
-        <v>0.02198751168433196</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="U20" s="17" t="s">
-        <v>283</v>
-      </c>
       <c r="V20" s="18">
-        <v>0.04014972506117992</v>
+        <v>0.01434807482027753</v>
       </c>
     </row>
   </sheetData>
